--- a/DataTables/Datas/Enemy/#EnemySkillInfo.xlsx
+++ b/DataTables/Datas/Enemy/#EnemySkillInfo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -587,6 +587,246 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ES003</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>铁锤重击</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>蓄力一击，造成{A}点伤害</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,18,false</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ES004</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>烈焰扫射</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>对所有目标造成{A}点伤害</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,5,true</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>AllEnemy</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ES005</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>铁壁加固</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>获得{D}点护甲，并减伤{V}%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>DefenseEffect,D,10,false;BuffEffect,B,ReduceDmg,30</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ES006</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>急袭斩</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>快速一击，造成{A}点伤害</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,4,false</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ES007</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>寒冰之握</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>造成{A}点伤害，对目标施加冰冻</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,3,false;BuffEffect,B,Chill,1</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ES008</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>终极燃烧</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>对所有目标造成{A}点伤害，并施加燃烧</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,8,true;BuffEffect,B,Burn,3</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AllEnemy</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ES009</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>战吼</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>获得{V}层力量</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>BuffEffect,B,Strength,2</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ES010</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>易伤诅咒</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>对目标施加{V}%易伤</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>BuffEffect,B,Vulnerable,50</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/DataTables/Datas/Enemy/#EnemySkillInfo.xlsx
+++ b/DataTables/Datas/Enemy/#EnemySkillInfo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>TargetType</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>TargetZone</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -489,6 +494,11 @@
           <t>TargetTypeEnum</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>TargetZoneEnum</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -526,6 +536,11 @@
           <t>SingleEnemy</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -556,6 +571,11 @@
           <t>SingleEnemy</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -586,6 +606,11 @@
           <t>Self</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -616,6 +641,11 @@
           <t>SingleEnemy</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -646,6 +676,11 @@
           <t>AllEnemy</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -676,6 +711,11 @@
           <t>Self</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
@@ -706,6 +746,11 @@
           <t>SingleEnemy</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
@@ -736,6 +781,11 @@
           <t>SingleEnemy</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -766,6 +816,11 @@
           <t>AllEnemy</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -796,6 +851,11 @@
           <t>Self</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
@@ -824,6 +884,151 @@
       <c r="G14" t="inlineStr">
         <is>
           <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ES011</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>重拳</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>造成{A}点伤害</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,12,false</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ES012</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>横扫</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>对所有目标造成{A}点伤害</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,8,true</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>AllEnemy</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ES013</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>战争咆哮</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>获得{V}层力量与{D}点护甲</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>BuffEffect,B,Strength,3;DefenseEffect,D,15,false</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ES014</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>湮灭一击</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>蓄力轰击，造成{A}点毁灭伤害；引导期间受到{V}点伤害即被打断</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,80,false;BuffEffect,B,Stagger,40</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>8</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Back</t>
         </is>
       </c>
     </row>

--- a/DataTables/Datas/Enemy/#EnemySkillInfo.xlsx
+++ b/DataTables/Datas/Enemy/#EnemySkillInfo.xlsx
@@ -2,39 +2,375 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="21">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -42,15 +378,305 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -403,7 +1029,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -414,7 +1039,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -678,7 +1303,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Back</t>
         </is>
       </c>
     </row>
@@ -740,11 +1365,6 @@
       </c>
       <c r="F10" t="n">
         <v>1</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SingleEnemy</t>
-        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>

--- a/DataTables/Datas/Enemy/#EnemySkillInfo.xlsx
+++ b/DataTables/Datas/Enemy/#EnemySkillInfo.xlsx
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>获得{D}点护甲，并减伤{V}%</t>
+          <t>获得{D}点护甲，并减伤{B}%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>获得{V}层力量</t>
+          <t>获得{B}层力量</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>对目标施加{V}%易伤</t>
+          <t>对目标施加{B}%易伤</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>获得{V}层力量与{D}点护甲</t>
+          <t>获得{B}层力量与{D}点护甲</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>蓄力轰击，造成{A}点毁灭伤害；引导期间受到{V}点伤害即被打断</t>
+          <t>蓄力轰击，造成{A}点毁灭伤害；引导期间受到{B}点伤害即被打断</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">

--- a/DataTables/Datas/Enemy/#EnemySkillInfo.xlsx
+++ b/DataTables/Datas/Enemy/#EnemySkillInfo.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -1652,6 +1652,356 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ES101</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>疾突</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>突刺前排，造成{A}点伤害</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,4,false</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ES102</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>掷石</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>投掷碎石袭击后排，造成{A}点伤害</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,4,false</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ES103</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>猎杀直觉</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>造成{A}点伤害，并施加{B}%易伤</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,6,false;BuffEffect,B,Vulnerable,25</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ES104</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>穷追猛打</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>造成{A}点伤害</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,9,false</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ES105</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>蓄能轰击</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>对前排所有目标造成{A}点伤害；引导期间受到{B}点伤害即被打断</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,10,true;BuffEffect,B,Stagger,15</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>AllEnemy</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ES106</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>榴散幕</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>对后排所有目标造成{A}点伤害；引导期间受到{B}点伤害即被打断</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,8,true;BuffEffect,B,Stagger,12</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>AllEnemy</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ES107</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>处决重锤</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>造成{A}点伤害</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,12,false</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ES108</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>震地横扫</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>对前排所有目标造成{A}点伤害</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,7,true</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>AllEnemy</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ES109</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>战意咆哮</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>获得{B}层力量与{D}点护甲</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>BuffEffect,B,Strength,2;DefenseEffect,D,10,false</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ES110</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>灭世震击</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>对所有目标造成{A}点伤害；引导期间受到{B}点伤害即被打断</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,14,true;BuffEffect,B,Stagger,30</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>7</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>AllEnemy</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/DataTables/Datas/Enemy/#EnemySkillInfo.xlsx
+++ b/DataTables/Datas/Enemy/#EnemySkillInfo.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -2002,6 +2002,531 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ESM01</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>杖击</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>对前排一名角色造成{A}点伤害。</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,4,false</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ESM02</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>塞签</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>将1张[解签]加入目标角色的手牌。</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AddToHandEffect,N,Extra006,1</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ESM03</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>摸索祷词</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>对后排一名角色造成{A}点伤害。</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,6,false</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ESM04</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>盲签训诫</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>对后排一名角色造成{A}点伤害，将1张[解签]加入其手牌。</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,3,false;AddToHandEffect,N,Extra006,1</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ESM05</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>戒尺横扫</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>对前排所有角色造成{A}点伤害。</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,7,true</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>AllEnemy</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ESM06</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>钟下裁定</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>对目标角色造成{A}点伤害，将1张[解签]加入其手牌；引导期间受到{B}点伤害即被打断。</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,8,false;AddToHandEffect,N,Extra006,1;BuffEffect,B,Stagger,14</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ESM07</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>封口裁决</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>对目标角色造成{A}点伤害。</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,10,false</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ESM08</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>戒律护身</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>获得{D}点护甲和{B}层力量。</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>DefenseEffect,D,8,false;BuffEffect,B,Strength,1</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ESM09</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>大斋戒</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>对目标角色造成{A}点伤害，将1张[解签]加入其手牌；引导期间受到{B}点伤害即被打断。</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,12,false;AddToHandEffect,N,Extra006,1;BuffEffect,B,Stagger,18</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>5</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ESW01</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>弹指</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>对前排一名角色造成{A}点伤害。</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,4,false</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ESW02</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>掷骨</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>对后排一名角色造成{A}点伤害。</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,4,false</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ESW03</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>嗅血</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>对目标角色造成{A}点伤害。</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,6,false</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ESW04</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>扑食</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>对目标角色造成{A}点伤害。</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,10,false</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ESW05</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>轮臂</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>对前排一名角色造成3次{A}点伤害。</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,3,false;AttackEffect,A,3,false;AttackEffect,A,3,false</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>3</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ESW06</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>献臂冲锋</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>对后排所有角色造成{A}点伤害；引导期间受到{B}点伤害即被打断。</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AttackEffect,A,12,true;BuffEffect,B,Stagger,16</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>5</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>AllEnemy</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
